--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-slurry.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-slurry.xlsx
@@ -1,32 +1,216 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DA6259-011F-40E0-B3F8-B053B1F44E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Ark1" sheetId="1" r:id="rId1"/>
+    <sheet name="TAN" sheetId="1" r:id="rId1"/>
+    <sheet name="DM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={3010D286-DD46-4595-B85E-FCD64EF9B2C1}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{3010D286-DD46-4595-B85E-FCD64EF9B2C1}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    SL = (cattle) slurry
+STD = ammonum carbonat </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={538B5E43-2735-419A-8A4A-2788BC0D6CD4}</author>
+  </authors>
+  <commentList>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{538B5E43-2735-419A-8A4A-2788BC0D6CD4}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    %DM during field exp were also around 6-7 % 
+I am yet again surprised the variance in the acidified samples are smaller, however in this case it might be better explaned by the lower mass of these samples</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>m(sample) [g]</t>
+  </si>
+  <si>
+    <t>c NH4-N (diluted) [mg/L]</t>
+  </si>
+  <si>
+    <t>m expected [g]</t>
+  </si>
+  <si>
+    <t>Dilution factor [-]</t>
+  </si>
+  <si>
+    <t>NH4-N (sample) [g/L]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NH4-N (sample) [g/L] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Mean </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NH4-N (sample) [g/L] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stdev</t>
+    </r>
+  </si>
+  <si>
+    <t>STD1</t>
+  </si>
+  <si>
+    <t>STD2</t>
+  </si>
+  <si>
+    <t>SL1</t>
+  </si>
+  <si>
+    <t>SL2</t>
+  </si>
+  <si>
+    <t>SL3</t>
+  </si>
+  <si>
+    <t>STD3</t>
+  </si>
+  <si>
+    <t>pH</t>
+  </si>
+  <si>
+    <t>m(alue) [g]</t>
+  </si>
+  <si>
+    <t>m(wet + alue) [g]</t>
+  </si>
+  <si>
+    <t>m(wet)</t>
+  </si>
+  <si>
+    <t>m(dry + alue) [g]</t>
+  </si>
+  <si>
+    <t>m(dry)</t>
+  </si>
+  <si>
+    <t>%DM</t>
+  </si>
+  <si>
+    <t>%DM avg</t>
+  </si>
+  <si>
+    <t>%DM std-dev</t>
+  </si>
+  <si>
+    <t>ML1</t>
+  </si>
+  <si>
+    <t>ML2</t>
+  </si>
+  <si>
+    <t>ML3</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +233,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -66,6 +254,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Mikael Løvig Larsen" id="{FCAAED7B-F5F1-4553-9146-85CC0A69F825}" userId="S::au705323@uni.au.dk::501b5c6e-34b9-41fc-bcf2-dc0650cde639" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -329,11 +523,397 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2026-02-22T14:16:25.16" personId="{FCAAED7B-F5F1-4553-9146-85CC0A69F825}" id="{3010D286-DD46-4595-B85E-FCD64EF9B2C1}">
+    <text xml:space="preserve">SL = (cattle) slurry
+STD = ammonum carbonat </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="H1" dT="2026-02-25T10:01:20.20" personId="{FCAAED7B-F5F1-4553-9146-85CC0A69F825}" id="{538B5E43-2735-419A-8A4A-2788BC0D6CD4}">
+    <text>%DM during field exp were also around 6-7 % 
+I am yet again surprised the variance in the acidified samples are smaller, however in this case it might be better explaned by the lower mass of these samples</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>7.18</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="D2">
+        <v>46</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2" s="3">
+        <f>((D2*E2*F2)/C2)/1000</f>
+        <v>2.2136669874879695</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>7.18</v>
+      </c>
+      <c r="C3">
+        <v>1.0096000000000001</v>
+      </c>
+      <c r="D3">
+        <v>44</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>50</v>
+      </c>
+      <c r="G3" s="3">
+        <f>((D3*E3*F3)/C3)/1000</f>
+        <v>2.1790808240887478</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>7.18</v>
+      </c>
+      <c r="C4">
+        <v>1.0019</v>
+      </c>
+      <c r="D4">
+        <v>43</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4" s="3">
+        <f>((D4*E4*F4)/C4)/1000</f>
+        <v>2.1459227467811162</v>
+      </c>
+      <c r="H4" s="2">
+        <f>AVERAGE(G2:G4)</f>
+        <v>2.1795568527859444</v>
+      </c>
+      <c r="I4">
+        <f>_xlfn.STDEV.P(G2:G4)</f>
+        <v>2.7658518756764474E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>8.07</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.0109999999999999</v>
+      </c>
+      <c r="D5">
+        <v>78</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5" s="3">
+        <f>((D5*E5*F5)/C5)/1000</f>
+        <v>3.8575667655786354</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>8.07</v>
+      </c>
+      <c r="C6">
+        <v>1.0321</v>
+      </c>
+      <c r="D6">
+        <v>93</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6" s="3">
+        <f>((D6*E6*F6)/C6)/1000</f>
+        <v>4.5053773859122179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>8.07</v>
+      </c>
+      <c r="C7">
+        <v>1.0082</v>
+      </c>
+      <c r="D7">
+        <v>88</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7" s="3">
+        <f>((D7*E7*F7)/C7)/1000</f>
+        <v>4.3642134497123592</v>
+      </c>
+      <c r="H7" s="3">
+        <f>AVERAGE(G5:G7)</f>
+        <v>4.2423858670677381</v>
+      </c>
+      <c r="I7">
+        <f>_xlfn.STDEV.P(G5:G7)</f>
+        <v>0.27814399133544643</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D8" s="2"/>
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D9" s="2"/>
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D10" s="2"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D11" s="2"/>
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D12" s="2"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A322F488-66DC-4E6C-A2BD-1AE1E849C347}">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>4.2969999999999997</v>
+      </c>
+      <c r="C2">
+        <v>38.987000000000002</v>
+      </c>
+      <c r="D2">
+        <f>C2-B2</f>
+        <v>34.690000000000005</v>
+      </c>
+      <c r="F2">
+        <f>E2-B2</f>
+        <v>-4.2969999999999997</v>
+      </c>
+      <c r="G2" s="2">
+        <f>(F2/D2)*100</f>
+        <v>-12.386855001441335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3">
+        <v>4.3070000000000004</v>
+      </c>
+      <c r="C3">
+        <v>47.526000000000003</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D10" si="0">C3-B3</f>
+        <v>43.219000000000001</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3">
+        <f t="shared" ref="F3:F10" si="1">E3-B3</f>
+        <v>-4.3070000000000004</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G10" si="2">(F3/D3)*100</f>
+        <v>-9.9655244221291568</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>4.2949999999999999</v>
+      </c>
+      <c r="C4" s="2">
+        <v>64.37</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>60.075000000000003</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>-4.2949999999999999</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="2"/>
+        <v>-7.1493965875988348</v>
+      </c>
+      <c r="H4" s="4">
+        <f>AVERAGE(G2:G4)</f>
+        <v>-9.8339253370564421</v>
+      </c>
+      <c r="I4" s="2">
+        <f>_xlfn.STDEV.P(G2:G4)</f>
+        <v>2.1402073729082711</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G10" s="2"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-slurry.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-slurry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4DA6259-011F-40E0-B3F8-B053B1F44E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1DF4EA-4458-4EE4-8683-A773EEB3553A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAN" sheetId="1" r:id="rId1"/>
@@ -55,25 +55,6 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={538B5E43-2735-419A-8A4A-2788BC0D6CD4}</author>
-  </authors>
-  <commentList>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{538B5E43-2735-419A-8A4A-2788BC0D6CD4}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    %DM during field exp were also around 6-7 % 
-I am yet again surprised the variance in the acidified samples are smaller, however in this case it might be better explaned by the lower mass of these samples</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
@@ -190,7 +171,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,12 +186,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -532,15 +507,6 @@
 </ThreadedComments>
 </file>
 
-<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="H1" dT="2026-02-25T10:01:20.20" personId="{FCAAED7B-F5F1-4553-9146-85CC0A69F825}" id="{538B5E43-2735-419A-8A4A-2788BC0D6CD4}">
-    <text>%DM during field exp were also around 6-7 % 
-I am yet again surprised the variance in the acidified samples are smaller, however in this case it might be better explaned by the lower mass of these samples</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I12"/>
@@ -603,7 +569,7 @@
         <v>50</v>
       </c>
       <c r="G2" s="3">
-        <f>((D2*E2*F2)/C2)/1000</f>
+        <f t="shared" ref="G2:G7" si="0">((D2*E2*F2)/C2)/1000</f>
         <v>2.2136669874879695</v>
       </c>
     </row>
@@ -627,7 +593,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="3">
-        <f>((D3*E3*F3)/C3)/1000</f>
+        <f t="shared" si="0"/>
         <v>2.1790808240887478</v>
       </c>
     </row>
@@ -651,7 +617,7 @@
         <v>50</v>
       </c>
       <c r="G4" s="3">
-        <f>((D4*E4*F4)/C4)/1000</f>
+        <f t="shared" si="0"/>
         <v>2.1459227467811162</v>
       </c>
       <c r="H4" s="2">
@@ -683,7 +649,7 @@
         <v>50</v>
       </c>
       <c r="G5" s="3">
-        <f>((D5*E5*F5)/C5)/1000</f>
+        <f t="shared" si="0"/>
         <v>3.8575667655786354</v>
       </c>
     </row>
@@ -707,7 +673,7 @@
         <v>50</v>
       </c>
       <c r="G6" s="3">
-        <f>((D6*E6*F6)/C6)/1000</f>
+        <f t="shared" si="0"/>
         <v>4.5053773859122179</v>
       </c>
     </row>
@@ -731,7 +697,7 @@
         <v>50</v>
       </c>
       <c r="G7" s="3">
-        <f>((D7*E7*F7)/C7)/1000</f>
+        <f t="shared" si="0"/>
         <v>4.3642134497123592</v>
       </c>
       <c r="H7" s="3">
@@ -772,7 +738,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A322F488-66DC-4E6C-A2BD-1AE1E849C347}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A322F488-66DC-4E6C-A2BD-1AE1E849C347}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -824,13 +790,16 @@
         <f>C2-B2</f>
         <v>34.690000000000005</v>
       </c>
+      <c r="E2">
+        <v>6.6029999999999998</v>
+      </c>
       <c r="F2">
         <f>E2-B2</f>
-        <v>-4.2969999999999997</v>
+        <v>2.306</v>
       </c>
       <c r="G2" s="2">
         <f>(F2/D2)*100</f>
-        <v>-12.386855001441335</v>
+        <v>6.6474488325165737</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -844,17 +813,19 @@
         <v>47.526000000000003</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D10" si="0">C3-B3</f>
+        <f t="shared" ref="D3:D4" si="0">C3-B3</f>
         <v>43.219000000000001</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="2">
+        <v>7.2389999999999999</v>
+      </c>
       <c r="F3">
-        <f t="shared" ref="F3:F10" si="1">E3-B3</f>
-        <v>-4.3070000000000004</v>
+        <f t="shared" ref="F3:F4" si="1">E3-B3</f>
+        <v>2.9319999999999995</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G10" si="2">(F3/D3)*100</f>
-        <v>-9.9655244221291568</v>
+        <f t="shared" ref="G3:G4" si="2">(F3/D3)*100</f>
+        <v>6.7840533098868532</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -871,21 +842,24 @@
         <f t="shared" si="0"/>
         <v>60.075000000000003</v>
       </c>
+      <c r="E4">
+        <v>8.4489999999999998</v>
+      </c>
       <c r="F4">
         <f t="shared" si="1"/>
-        <v>-4.2949999999999999</v>
+        <v>4.1539999999999999</v>
       </c>
       <c r="G4" s="2">
         <f t="shared" si="2"/>
-        <v>-7.1493965875988348</v>
+        <v>6.9146899708697456</v>
       </c>
       <c r="H4" s="4">
         <f>AVERAGE(G2:G4)</f>
-        <v>-9.8339253370564421</v>
+        <v>6.7820640377577242</v>
       </c>
       <c r="I4" s="2">
         <f>_xlfn.STDEV.P(G2:G4)</f>
-        <v>2.1402073729082711</v>
+        <v>0.10910980527211286</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -914,6 +888,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-slurry.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-slurry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1DF4EA-4458-4EE4-8683-A773EEB3553A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B521F1-787B-4B25-8B9F-9FA16D5401CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TAN" sheetId="1" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <t>m(sample) [g]</t>
   </si>
   <si>
-    <t>c NH4-N (diluted) [mg/L]</t>
-  </si>
-  <si>
     <t>m expected [g]</t>
   </si>
   <si>
@@ -160,6 +157,9 @@
   </si>
   <si>
     <t>ML3</t>
+  </si>
+  <si>
+    <t>NH4-N (diluted) [mg/L]</t>
   </si>
 </sst>
 </file>
@@ -208,12 +208,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,40 +521,41 @@
     <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>7.18</v>
@@ -575,7 +579,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>7.18</v>
@@ -599,7 +603,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>7.18</v>
@@ -631,7 +635,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>8.07</v>
@@ -655,7 +659,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>8.07</v>
@@ -679,7 +683,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>8.07</v>
@@ -752,33 +756,33 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>21</v>
-      </c>
-      <c r="I1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>4.2969999999999997</v>
@@ -804,7 +808,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>4.3070000000000004</v>
@@ -830,7 +834,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>4.2949999999999999</v>

--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-slurry.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-slurry.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B521F1-787B-4B25-8B9F-9FA16D5401CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3596F746-7308-4EEA-934D-B841EEC39D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,7 +573,7 @@
         <v>50</v>
       </c>
       <c r="G2" s="3">
-        <f t="shared" ref="G2:G7" si="0">((D2*E2*F2)/C2)/1000</f>
+        <f>((D2*E2*F2)/C2)/1000</f>
         <v>2.2136669874879695</v>
       </c>
     </row>
@@ -597,7 +597,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G2:G7" si="0">((D3*E3*F3)/C3)/1000</f>
         <v>2.1790808240887478</v>
       </c>
     </row>

--- a/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-slurry.xlsx
+++ b/Lab-trails/2026-04-14-Density-exp/2026-04-14-density-exp-slurry.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-04-14-Density-exp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3596F746-7308-4EEA-934D-B841EEC39D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31F5485-2B0B-417B-AE11-6FAFD9727561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -597,7 +597,7 @@
         <v>50</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G2:G7" si="0">((D3*E3*F3)/C3)/1000</f>
+        <f t="shared" ref="G3:G7" si="0">((D3*E3*F3)/C3)/1000</f>
         <v>2.1790808240887478</v>
       </c>
     </row>
@@ -624,11 +624,11 @@
         <f t="shared" si="0"/>
         <v>2.1459227467811162</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <f>AVERAGE(G2:G4)</f>
         <v>2.1795568527859444</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="3">
         <f>_xlfn.STDEV.P(G2:G4)</f>
         <v>2.7658518756764474E-2</v>
       </c>
@@ -708,7 +708,7 @@
         <f>AVERAGE(G5:G7)</f>
         <v>4.2423858670677381</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="3">
         <f>_xlfn.STDEV.P(G5:G7)</f>
         <v>0.27814399133544643</v>
       </c>
@@ -749,6 +749,7 @@
     <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -857,11 +858,11 @@
         <f t="shared" si="2"/>
         <v>6.9146899708697456</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <f>AVERAGE(G2:G4)</f>
         <v>6.7820640377577242</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="3">
         <f>_xlfn.STDEV.P(G2:G4)</f>
         <v>0.10910980527211286</v>
       </c>
